--- a/templates/order-import-template.xlsx
+++ b/templates/order-import-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="77">
   <si>
     <t>ORDER DATE</t>
   </si>
@@ -176,7 +176,7 @@
     <t>Only ORDER DATE, ORDER NO. and PARTY NAME are compulsory.</t>
   </si>
   <si>
-    <t>Plus FABRIC, DESIGN NO and QTY (MTR) on every design line. Everything else can be left empty.</t>
+    <t>Plus FABRIC and QTY (MTR) on every design line. Everything else can be left empty.</t>
   </si>
   <si>
     <t>One row per DESIGN, not per order.</t>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>That column is formatted as text so 01 stays 01 instead of becoming 1. Do not reformat it.</t>
+  </si>
+  <si>
+    <t>DESIGN NO: blank or - is fine.</t>
+  </si>
+  <si>
+    <t>A plain or solid fabric has no design number. Leave it empty or write -, and the line imports as "-" rather than being refused.</t>
   </si>
   <si>
     <t>AMOUNT is CHECKED, never imported.</t>
@@ -1077,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -1220,6 +1226,14 @@
         <v>74</v>
       </c>
     </row>
+    <row r="20" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
